--- a/data-raw/overzicht_referentiebestanden.xlsx
+++ b/data-raw/overzicht_referentiebestanden.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\waterplanten\data-raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A058E7-D80E-4B59-8CB1-28A9B1E6F149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9C80D6-8627-446A-9073-FE441B5992DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E372719C-86F7-4879-8696-6B1EE6242496}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="8745" xr2:uid="{E372719C-86F7-4879-8696-6B1EE6242496}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
+    <sheet name="Toelichting" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$D$26</definedName>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="59">
   <si>
     <t>bestandsnaam</t>
   </si>
@@ -207,6 +208,15 @@
   </si>
   <si>
     <t>data-raw/preferenties/Preferentietabel 9 chloride in oppervlaktewater.xlsx</t>
+  </si>
+  <si>
+    <t>omrekenfactor_naar_mg_l</t>
+  </si>
+  <si>
+    <t>De omrekenfactor voor N en P componenten is bedoeld voor mg/l uitgedrukt in P of N</t>
+  </si>
+  <si>
+    <t>De omrekenfactor is bedoeld om mee te vermenigvuldigen</t>
   </si>
 </sst>
 </file>
@@ -578,16 +588,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0938D54A-21AE-4F12-824A-DACDD9F86555}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -600,8 +611,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -615,7 +629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -628,8 +642,11 @@
       <c r="D3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>3.9098300000000002E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -642,8 +659,11 @@
       <c r="D4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>9.6062599999999998E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -657,7 +677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -671,7 +691,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -684,8 +704,11 @@
       <c r="D7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>1.40067E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -698,8 +721,11 @@
       <c r="D8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>6.1016799999999996E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -712,8 +738,11 @@
       <c r="D9" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>4.40095E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -726,8 +755,11 @@
       <c r="D10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>3.0973799999999999E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -740,8 +772,11 @@
       <c r="D11" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>1.40067E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -755,7 +790,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -768,8 +803,11 @@
       <c r="D13" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>4.40095E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -782,8 +820,11 @@
       <c r="D14" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>4.0078000000000003E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -796,8 +837,11 @@
       <c r="D15" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>3.5453000000000005E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -810,8 +854,11 @@
       <c r="D16" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>5.5844999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -824,8 +871,11 @@
       <c r="D17" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>3.2064999999999996E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -839,7 +889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -853,7 +903,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -866,8 +916,11 @@
       <c r="D20" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>6.1016799999999996E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -881,7 +934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -894,8 +947,11 @@
       <c r="D22" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>3.0973799999999999E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -908,8 +964,11 @@
       <c r="D23" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>3.0973799999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>53</v>
       </c>
@@ -922,8 +981,11 @@
       <c r="D24" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>1.40067E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -936,8 +998,11 @@
       <c r="D25" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25">
+        <v>4.0078000000000003E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -949,10 +1014,33 @@
       </c>
       <c r="D26" t="s">
         <v>4</v>
+      </c>
+      <c r="E26">
+        <v>3.5453000000000005E-2</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D26" xr:uid="{0938D54A-21AE-4F12-824A-DACDD9F86555}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E87B93D3-467A-4CA0-81C0-B2CE2362CD0B}">
+  <dimension ref="A2:A3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>